--- a/Data/EXCEL/Transfer/salemon/202208/8215-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8215-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84CEFA74-FDAC-4172-B748-E73DD3495486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8176A7A1-8E79-41DD-AB98-760E8F951499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8215-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,20 +1227,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q240"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="6" width="10.125" customWidth="1"/>
-    <col min="7" max="7" width="11.125" customWidth="1"/>
-    <col min="8" max="8" width="10.125" customWidth="1"/>
-    <col min="9" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="13" width="10.125" customWidth="1"/>
-    <col min="14" max="14" width="9.5" customWidth="1"/>
-    <col min="15" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="14.125" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
+    <col min="10" max="13" width="14.125" customWidth="1"/>
+    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="17" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1259,7 +1266,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1298,7 +1305,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1341,7 +1348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1380,7 +1387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1433,7 +1440,7 @@
         <v>-2.54</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1486,7 +1493,7 @@
         <v>-1.71</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1539,7 +1546,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1592,7 +1599,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1645,7 +1652,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1698,7 +1705,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1751,7 +1758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1804,7 +1811,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1857,7 +1864,7 @@
         <v>9.51</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1910,7 +1917,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1963,7 +1970,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2016,7 +2023,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2069,7 +2076,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2122,7 +2129,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2175,7 +2182,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2228,7 +2235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2281,7 +2288,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2334,7 +2341,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2387,7 +2394,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2440,7 +2447,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2493,7 +2500,7 @@
         <v>7.93</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2546,7 +2553,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2599,7 +2606,7 @@
         <v>5.27</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2652,7 +2659,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2705,7 +2712,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2758,7 +2765,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2811,7 +2818,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2864,7 +2871,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2917,7 +2924,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2970,7 +2977,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3023,7 +3030,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3076,7 +3083,7 @@
         <v>-8.41</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3129,7 +3136,7 @@
         <v>9.24</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3182,7 +3189,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3235,7 +3242,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3288,7 +3295,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3341,7 +3348,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3394,7 +3401,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3447,7 +3454,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3500,7 +3507,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3553,7 +3560,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3606,7 +3613,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3659,7 +3666,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3712,7 +3719,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3765,7 +3772,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3818,7 +3825,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3871,7 +3878,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3924,7 +3931,7 @@
         <v>9.68</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3977,7 +3984,7 @@
         <v>8.07</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4030,7 +4037,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4083,7 +4090,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4136,7 +4143,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4189,7 +4196,7 @@
         <v>-1.0900000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4242,7 +4249,7 @@
         <v>-3.83</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4295,7 +4302,7 @@
         <v>-7.17</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4348,7 +4355,7 @@
         <v>-6.8</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4401,7 +4408,7 @@
         <v>-12.7</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4454,7 +4461,7 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4507,7 +4514,7 @@
         <v>-11.4</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4560,7 +4567,7 @@
         <v>-10.6</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4613,7 +4620,7 @@
         <v>-10.4</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4666,7 +4673,7 @@
         <v>-9.8000000000000007</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4719,7 +4726,7 @@
         <v>-9.08</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4772,7 +4779,7 @@
         <v>-8.33</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4825,7 +4832,7 @@
         <v>-6.48</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4878,7 +4885,7 @@
         <v>-3.27</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4931,7 +4938,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4984,7 +4991,7 @@
         <v>-1.51</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5037,7 +5044,7 @@
         <v>-12.8</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5090,7 +5097,7 @@
         <v>-14.2</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5143,7 +5150,7 @@
         <v>-14.4</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5196,7 +5203,7 @@
         <v>-14.4</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5249,7 +5256,7 @@
         <v>-14.7</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5302,7 +5309,7 @@
         <v>-15.6</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5355,7 +5362,7 @@
         <v>-16.2</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5408,7 +5415,7 @@
         <v>-16.7</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5461,7 +5468,7 @@
         <v>-16.399999999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5514,7 +5521,7 @@
         <v>-17.100000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5567,7 +5574,7 @@
         <v>-17.399999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5620,7 +5627,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5673,7 +5680,7 @@
         <v>-11.4</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5726,7 +5733,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5779,7 +5786,7 @@
         <v>-10.7</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5832,7 +5839,7 @@
         <v>-10.199999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5885,7 +5892,7 @@
         <v>-9.93</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5938,7 +5945,7 @@
         <v>-9.4700000000000006</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5991,7 +5998,7 @@
         <v>-8.84</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6044,7 +6051,7 @@
         <v>-7.04</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6097,7 +6104,7 @@
         <v>-5.73</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6150,7 +6157,7 @@
         <v>-4.67</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6203,7 +6210,7 @@
         <v>-3.24</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6256,7 +6263,7 @@
         <v>-8.1999999999999993</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6309,7 +6316,7 @@
         <v>-8.56</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6362,7 +6369,7 @@
         <v>-8.5500000000000007</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6415,7 +6422,7 @@
         <v>-9.3800000000000008</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6468,7 +6475,7 @@
         <v>-10.7</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6521,7 +6528,7 @@
         <v>-11.5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6574,7 +6581,7 @@
         <v>-12.1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6627,7 +6634,7 @@
         <v>-12.3</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6680,7 +6687,7 @@
         <v>-12.1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6733,7 +6740,7 @@
         <v>-11.4</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6786,7 +6793,7 @@
         <v>-8.59</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6839,7 +6846,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6892,7 +6899,7 @@
         <v>-4.1399999999999997</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6945,7 +6952,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -6998,7 +7005,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7051,7 +7058,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7104,7 +7111,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7157,7 +7164,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7210,7 +7217,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7263,7 +7270,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7316,7 +7323,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7369,7 +7376,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7422,7 +7429,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7475,7 +7482,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7528,7 +7535,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7581,7 +7588,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7634,7 +7641,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7687,7 +7694,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7740,7 +7747,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7793,7 +7800,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7846,7 +7853,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7899,7 +7906,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7952,7 +7959,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8005,7 +8012,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8058,7 +8065,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8111,7 +8118,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8164,7 +8171,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8217,7 +8224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8270,7 +8277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8323,7 +8330,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8376,7 +8383,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8429,7 +8436,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8482,7 +8489,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8535,7 +8542,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8588,7 +8595,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8641,7 +8648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8694,7 +8701,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8747,7 +8754,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8800,7 +8807,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8853,7 +8860,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8906,7 +8913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8959,7 +8966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9012,7 +9019,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>40391</v>
       </c>
@@ -9065,7 +9072,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>40360</v>
       </c>
@@ -9118,7 +9125,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>40330</v>
       </c>
@@ -9171,7 +9178,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>40299</v>
       </c>
@@ -9224,7 +9231,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="5" customFormat="1">
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>40269</v>
       </c>
@@ -9277,7 +9284,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" s="5" customFormat="1">
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>40238</v>
       </c>
@@ -9330,7 +9337,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" s="5" customFormat="1">
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>40210</v>
       </c>
@@ -9383,7 +9390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" s="5" customFormat="1">
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>40179</v>
       </c>
@@ -9436,7 +9443,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1">
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>40148</v>
       </c>
@@ -9489,7 +9496,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1">
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>40118</v>
       </c>
@@ -9542,7 +9549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="5" customFormat="1">
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>40087</v>
       </c>
@@ -9595,7 +9602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="5" customFormat="1">
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>40057</v>
       </c>
@@ -9648,7 +9655,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:17" s="5" customFormat="1">
+    <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>40026</v>
       </c>
@@ -9701,7 +9708,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:17" s="5" customFormat="1">
+    <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>39995</v>
       </c>
@@ -9754,7 +9761,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:17" s="5" customFormat="1">
+    <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>39965</v>
       </c>
@@ -9807,7 +9814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" s="5" customFormat="1">
+    <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>39934</v>
       </c>
@@ -9860,7 +9867,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:17" s="5" customFormat="1">
+    <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>39904</v>
       </c>
@@ -9913,7 +9920,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:17" s="5" customFormat="1">
+    <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>39873</v>
       </c>
@@ -9966,7 +9973,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:17" s="5" customFormat="1">
+    <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>39845</v>
       </c>
@@ -10019,7 +10026,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:17" s="5" customFormat="1">
+    <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>39814</v>
       </c>
@@ -10072,7 +10079,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:17" s="5" customFormat="1">
+    <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>39783</v>
       </c>
@@ -10125,7 +10132,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:17" s="5" customFormat="1">
+    <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>39753</v>
       </c>
@@ -10178,7 +10185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" s="5" customFormat="1">
+    <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>39722</v>
       </c>
@@ -10231,7 +10238,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:17" s="5" customFormat="1">
+    <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>39692</v>
       </c>
@@ -10284,7 +10291,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:17" s="5" customFormat="1">
+    <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>39661</v>
       </c>
@@ -10337,7 +10344,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:17" s="5" customFormat="1">
+    <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>39630</v>
       </c>
@@ -10390,7 +10397,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:17" s="5" customFormat="1">
+    <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>39600</v>
       </c>
@@ -10443,7 +10450,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:17" s="5" customFormat="1">
+    <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>39569</v>
       </c>
@@ -10496,7 +10503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:17" s="5" customFormat="1">
+    <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>39539</v>
       </c>
@@ -10549,7 +10556,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:17" s="5" customFormat="1">
+    <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>39508</v>
       </c>
@@ -10602,7 +10609,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:17" s="5" customFormat="1">
+    <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>39479</v>
       </c>
@@ -10655,7 +10662,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:17" s="5" customFormat="1">
+    <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>39448</v>
       </c>
@@ -10708,7 +10715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:17" s="5" customFormat="1">
+    <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>39417</v>
       </c>
@@ -10761,7 +10768,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:17" s="5" customFormat="1">
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>39387</v>
       </c>
@@ -10814,7 +10821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:17" s="5" customFormat="1">
+    <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>39356</v>
       </c>
@@ -10867,7 +10874,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:17" s="5" customFormat="1">
+    <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>39326</v>
       </c>
@@ -10920,7 +10927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:17" s="5" customFormat="1">
+    <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>39295</v>
       </c>
@@ -10973,7 +10980,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:17" s="5" customFormat="1">
+    <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>39264</v>
       </c>
@@ -11026,7 +11033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:17" s="5" customFormat="1">
+    <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>39234</v>
       </c>
@@ -11079,7 +11086,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:17" s="5" customFormat="1">
+    <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>39203</v>
       </c>
@@ -11132,7 +11139,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:17" s="5" customFormat="1">
+    <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>39173</v>
       </c>
@@ -11185,7 +11192,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:17" s="5" customFormat="1">
+    <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>39142</v>
       </c>
@@ -11238,7 +11245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:17" s="5" customFormat="1">
+    <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>39114</v>
       </c>
@@ -11291,7 +11298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:17" s="5" customFormat="1">
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>39083</v>
       </c>
@@ -11344,7 +11351,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:17" s="5" customFormat="1">
+    <row r="193" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>39052</v>
       </c>
@@ -11397,7 +11404,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" s="5" customFormat="1">
+    <row r="194" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>39022</v>
       </c>
@@ -11450,7 +11457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" s="5" customFormat="1">
+    <row r="195" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>38991</v>
       </c>
@@ -11503,7 +11510,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" s="5" customFormat="1">
+    <row r="196" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>38961</v>
       </c>
@@ -11556,7 +11563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" s="5" customFormat="1">
+    <row r="197" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>38930</v>
       </c>
@@ -11609,7 +11616,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" s="5" customFormat="1">
+    <row r="198" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>38899</v>
       </c>
@@ -11662,7 +11669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" s="5" customFormat="1">
+    <row r="199" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>38869</v>
       </c>
@@ -11715,7 +11722,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" s="5" customFormat="1">
+    <row r="200" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>38838</v>
       </c>
@@ -11768,7 +11775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" s="5" customFormat="1">
+    <row r="201" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>38808</v>
       </c>
@@ -11821,7 +11828,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" s="5" customFormat="1">
+    <row r="202" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>38777</v>
       </c>
@@ -11874,7 +11881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" s="5" customFormat="1">
+    <row r="203" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>38749</v>
       </c>
@@ -11927,7 +11934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" s="5" customFormat="1">
+    <row r="204" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>38718</v>
       </c>
@@ -11980,7 +11987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" s="5" customFormat="1">
+    <row r="205" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>38687</v>
       </c>
@@ -12033,7 +12040,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" s="5" customFormat="1">
+    <row r="206" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>38657</v>
       </c>
@@ -12086,7 +12093,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" s="5" customFormat="1">
+    <row r="207" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>38626</v>
       </c>
@@ -12139,7 +12146,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" s="5" customFormat="1">
+    <row r="208" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>38596</v>
       </c>
@@ -12192,7 +12199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" s="5" customFormat="1">
+    <row r="209" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>38565</v>
       </c>
@@ -12245,7 +12252,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" s="5" customFormat="1">
+    <row r="210" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>38534</v>
       </c>
@@ -12298,7 +12305,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" s="5" customFormat="1">
+    <row r="211" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>38504</v>
       </c>
@@ -12351,7 +12358,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" s="5" customFormat="1">
+    <row r="212" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>38473</v>
       </c>
@@ -12404,7 +12411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" s="5" customFormat="1">
+    <row r="213" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>38443</v>
       </c>
@@ -12457,7 +12464,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" s="5" customFormat="1">
+    <row r="214" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>38412</v>
       </c>
@@ -12510,7 +12517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" s="5" customFormat="1">
+    <row r="215" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>38384</v>
       </c>
@@ -12563,7 +12570,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" s="5" customFormat="1">
+    <row r="216" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>38353</v>
       </c>
@@ -12616,7 +12623,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" s="5" customFormat="1">
+    <row r="217" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>38322</v>
       </c>
@@ -12669,7 +12676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" s="5" customFormat="1">
+    <row r="218" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>38292</v>
       </c>
@@ -12722,7 +12729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" s="5" customFormat="1">
+    <row r="219" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>38261</v>
       </c>
@@ -12775,7 +12782,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" s="5" customFormat="1">
+    <row r="220" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>38231</v>
       </c>
@@ -12828,7 +12835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" s="5" customFormat="1">
+    <row r="221" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>38200</v>
       </c>
@@ -12881,7 +12888,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" s="5" customFormat="1">
+    <row r="222" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>38169</v>
       </c>
@@ -12934,7 +12941,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" s="5" customFormat="1">
+    <row r="223" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>38139</v>
       </c>
@@ -12987,7 +12994,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" s="5" customFormat="1">
+    <row r="224" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>38108</v>
       </c>
@@ -13040,7 +13047,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" s="5" customFormat="1">
+    <row r="225" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>38078</v>
       </c>
@@ -13093,7 +13100,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" s="5" customFormat="1">
+    <row r="226" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>38047</v>
       </c>
@@ -13146,7 +13153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" s="5" customFormat="1">
+    <row r="227" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>38018</v>
       </c>
@@ -13199,7 +13206,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="5" customFormat="1">
+    <row r="228" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>37987</v>
       </c>
@@ -13252,7 +13259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="5" customFormat="1">
+    <row r="229" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>37956</v>
       </c>
@@ -13305,7 +13312,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" s="5" customFormat="1">
+    <row r="230" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>37926</v>
       </c>
@@ -13358,7 +13365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" s="5" customFormat="1">
+    <row r="231" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>37895</v>
       </c>
@@ -13411,7 +13418,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" s="5" customFormat="1">
+    <row r="232" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>37865</v>
       </c>
@@ -13464,7 +13471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" s="5" customFormat="1">
+    <row r="233" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>37834</v>
       </c>
@@ -13517,7 +13524,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" s="5" customFormat="1">
+    <row r="234" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>37803</v>
       </c>
@@ -13570,7 +13577,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" s="5" customFormat="1">
+    <row r="235" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>37773</v>
       </c>
@@ -13623,7 +13630,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" s="5" customFormat="1">
+    <row r="236" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>37742</v>
       </c>
@@ -13676,7 +13683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" s="5" customFormat="1">
+    <row r="237" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>37712</v>
       </c>
@@ -13729,7 +13736,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" s="5" customFormat="1">
+    <row r="238" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>37681</v>
       </c>
@@ -13782,7 +13789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" s="5" customFormat="1">
+    <row r="239" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>37653</v>
       </c>
@@ -13835,7 +13842,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" s="5" customFormat="1">
+    <row r="240" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>37622</v>
       </c>
@@ -13903,7 +13910,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>